--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_prebrut_a_2019_nuble.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_prebrut_a_2019_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:03</t>
+    <t xml:space="preserve">2026-09-24 00:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -684,7 +684,7 @@
         <v>0.1</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>-0.45</v>
@@ -707,10 +707,10 @@
         <v>0.16</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-0.43</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="10">
@@ -730,7 +730,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>-0.27</v>
@@ -744,16 +744,16 @@
         <v>16</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>21</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.07</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>-0.01</v>
@@ -799,7 +799,7 @@
         <v>0.06</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>0.33</v>
@@ -819,10 +819,10 @@
         <v>21</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>-0.05</v>
@@ -845,7 +845,7 @@
         <v>-0.02</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>0.02</v>
